--- a/booking_forms/014_office_hours_appointment_form--booking_forms.xlsx
+++ b/booking_forms/014_office_hours_appointment_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'meeting_type',_'label':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'meeting_type', 'label': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'meeting_type',_'label':_'no_meeting'}</t>
+          <t>no_meeting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'meeting_type', 'label': 'No Meeting'}</t>
+          <t>No Meeting</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'meeting_type',_'label':_'office_hours'}</t>
+          <t>office_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'meeting_type', 'label': 'Office Hours'}</t>
+          <t>Office Hours</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'morning',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'morning', 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'afternoon',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'afternoon', 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'evening',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'evening', 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'weekend',_'label':_'weekend'}</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'weekend', 'label': 'Weekend'}</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'meeting_request',_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'meeting_request', 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'meeting_request',_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'meeting_request', 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'meeting_request',_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'meeting_request', 'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
